--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,91; 45,71</t>
+          <t>29,46; 44,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,1; 55,52</t>
+          <t>39,06; 55,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,66; 43,69</t>
+          <t>27,57; 44,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,97; 97,83</t>
+          <t>91,72; 97,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,09; 50,13</t>
+          <t>35,09; 49,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,87; 57,8</t>
+          <t>41,82; 57,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 47,21</t>
+          <t>31,44; 47,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,82; 98,27</t>
+          <t>91,65; 98,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,32; 45,39</t>
+          <t>34,78; 45,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,93; 54,28</t>
+          <t>43,45; 54,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,46; 43,88</t>
+          <t>31,71; 43,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,96; 97,6</t>
+          <t>93,35; 97,59</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,03; 45,7</t>
+          <t>31,56; 45,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,88; 58,04</t>
+          <t>43,77; 58,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,07; 51,86</t>
+          <t>39,15; 51,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,0; 98,02</t>
+          <t>93,09; 97,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,41; 48,17</t>
+          <t>35,08; 47,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,04; 57,14</t>
+          <t>43,61; 57,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 50,64</t>
+          <t>38,57; 51,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,02; 96,91</t>
+          <t>90,57; 96,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,6; 45,21</t>
+          <t>35,06; 44,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 55,04</t>
+          <t>45,86; 55,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,68; 49,45</t>
+          <t>40,6; 49,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,82; 96,77</t>
+          <t>92,76; 96,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,06; 50,06</t>
+          <t>35,19; 48,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,13; 53,68</t>
+          <t>38,69; 54,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,03; 44,54</t>
+          <t>30,24; 43,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92,43; 97,97</t>
+          <t>92,63; 97,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,42; 54,53</t>
+          <t>39,96; 54,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,5; 53,86</t>
+          <t>39,54; 55,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,51; 48,44</t>
+          <t>35,45; 49,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,07; 96,17</t>
+          <t>89,92; 96,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,05; 49,75</t>
+          <t>39,63; 50,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,53; 51,91</t>
+          <t>40,64; 51,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 44,74</t>
+          <t>35,4; 45,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,29; 96,4</t>
+          <t>92,38; 96,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,21; 47,73</t>
+          <t>34,06; 46,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,06; 49,83</t>
+          <t>35,97; 50,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,51; 53,81</t>
+          <t>40,59; 53,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,24; 96,21</t>
+          <t>88,96; 95,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,7; 48,84</t>
+          <t>35,45; 47,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,14; 52,49</t>
+          <t>38,55; 51,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,69; 44,13</t>
+          <t>31,26; 44,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,7; 97,48</t>
+          <t>91,33; 97,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,81; 45,62</t>
+          <t>36,01; 45,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 48,86</t>
+          <t>39,2; 48,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,74; 46,72</t>
+          <t>37,78; 46,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,88; 96,19</t>
+          <t>91,64; 96,17</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,09; 43,32</t>
+          <t>36,33; 43,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,23</t>
+          <t>43,1; 50,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,94; 45,67</t>
+          <t>39,05; 46,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,52; 96,48</t>
+          <t>93,65; 96,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,47</t>
+          <t>39,46; 46,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,3; 51,32</t>
+          <t>44,4; 51,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,67</t>
+          <t>37,91; 44,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,08; 96,1</t>
+          <t>92,96; 96,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,83; 43,63</t>
+          <t>38,91; 43,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,8; 49,78</t>
+          <t>44,72; 50,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,31; 44,27</t>
+          <t>39,18; 44,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,9</t>
+          <t>93,79; 95,86</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>39335</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31755</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111992</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49766</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56308</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>135087</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>89101</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101934</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72904</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>247080</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>30997; 46893</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37939; 53842</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24837; 39971</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>107567; 114389</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>41510; 59092</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>47052; 64623</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32911; 50078</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>128687; 138344</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>77724; 101781</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>91083; 113649</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>61757; 85534</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>240555; 251480</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>47853</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69312</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>182854</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58073</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77801</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77990</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>241013</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>105926</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143842</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>147302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>423869</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39436; 56522</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56461; 75451</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59477; 78426</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177345; 186318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>49370; 67402</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67406; 88260</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>67622; 89703</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>230995; 247227</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>93149; 117584</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>130032; 157692</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>132845; 161366</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>413272; 431216</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>45742</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48307</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43630</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>182173</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52737</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54699</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56216</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>173656</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>98479</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103006</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>99846</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>355829</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>37952; 52775</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40562; 56890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35242; 51169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>176373; 186513</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>44986; 61601</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>46171; 64835</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47099; 65641</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>166612; 178559</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>87356; 110286</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>90080; 114116</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>88277; 112399</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>347047; 362966</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>67215</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77977</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65657</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70265</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59262</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>172412</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>132872</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>132684</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>137239</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>329061</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>56308; 77528</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52523; 74273</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67722; 89462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>149413; 161149</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>55642; 75256</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>59734; 80096</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>49449; 69764</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>165529; 177043</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>116055; 146256</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>117960; 146438</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>122804; 152654</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>320023; 335823</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>200145</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222394</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>222674</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>633667</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>722169</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>426378</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>481467</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>457292</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1355836</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>182877; 216941</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>205564; 239769</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>205187; 245939</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>623857; 643158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>208567; 243856</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>239227; 276099</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>216460; 254440</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>708305; 732249</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>401501; 451997</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>454290; 509320</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>429534; 483422</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1339500; 1368932</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,46; 44,57</t>
+          <t>30,25; 45,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,06; 55,43</t>
+          <t>38,52; 56,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 44,37</t>
+          <t>27,7; 44,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,72; 97,53</t>
+          <t>92,06; 97,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,09; 49,96</t>
+          <t>34,27; 50,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,82; 57,44</t>
+          <t>42,56; 58,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,44; 47,84</t>
+          <t>31,67; 48,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,65; 98,53</t>
+          <t>91,38; 98,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,78; 45,54</t>
+          <t>34,9; 45,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,45; 54,21</t>
+          <t>42,93; 54,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,71; 43,92</t>
+          <t>31,64; 43,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,35; 97,59</t>
+          <t>93,1; 97,67</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 45,23</t>
+          <t>32,0; 45,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,77; 58,5</t>
+          <t>44,43; 58,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,15; 51,62</t>
+          <t>39,48; 51,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,09; 97,8</t>
+          <t>93,1; 97,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,08; 47,89</t>
+          <t>35,35; 48,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,61; 57,11</t>
+          <t>43,76; 56,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,57; 51,17</t>
+          <t>38,66; 50,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,57; 96,94</t>
+          <t>91,09; 96,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 44,25</t>
+          <t>35,32; 44,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,86; 55,62</t>
+          <t>46,0; 55,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,6; 49,31</t>
+          <t>40,44; 49,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,76; 96,78</t>
+          <t>92,57; 96,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,19; 48,93</t>
+          <t>34,9; 50,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,69; 54,26</t>
+          <t>38,77; 53,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 43,9</t>
+          <t>30,19; 44,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92,63; 97,96</t>
+          <t>92,09; 97,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,96; 54,72</t>
+          <t>39,59; 53,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,54; 55,52</t>
+          <t>39,97; 55,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,45; 49,41</t>
+          <t>35,49; 49,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,92; 96,37</t>
+          <t>89,57; 96,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,63; 50,03</t>
+          <t>39,44; 49,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,64; 51,49</t>
+          <t>41,12; 51,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,4; 45,07</t>
+          <t>35,32; 44,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,38; 96,61</t>
+          <t>92,46; 96,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,06; 46,89</t>
+          <t>34,43; 47,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,97; 50,87</t>
+          <t>36,03; 49,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,59; 53,63</t>
+          <t>39,47; 52,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,96; 95,94</t>
+          <t>89,27; 96,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 47,95</t>
+          <t>35,19; 47,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,55; 51,69</t>
+          <t>38,53; 52,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 44,1</t>
+          <t>31,35; 44,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,33; 97,69</t>
+          <t>92,02; 97,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,01; 45,38</t>
+          <t>36,78; 45,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 48,66</t>
+          <t>39,44; 48,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,78; 46,97</t>
+          <t>37,76; 47,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,64; 96,17</t>
+          <t>91,65; 96,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,33; 43,1</t>
+          <t>35,99; 43,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 50,27</t>
+          <t>42,91; 50,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,05; 46,81</t>
+          <t>39,25; 45,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,65; 96,55</t>
+          <t>93,73; 96,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,14</t>
+          <t>39,5; 46,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,4; 51,25</t>
+          <t>44,59; 51,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,56</t>
+          <t>37,51; 44,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,96; 96,1</t>
+          <t>93,06; 96,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,91; 43,8</t>
+          <t>38,72; 43,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,72; 50,14</t>
+          <t>44,74; 49,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,18; 44,09</t>
+          <t>39,26; 44,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,79; 95,86</t>
+          <t>93,84; 95,98</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30997; 46893</t>
+          <t>31830; 47647</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37939; 53842</t>
+          <t>37410; 55236</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24837; 39971</t>
+          <t>24955; 40284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107567; 114389</t>
+          <t>107971; 114675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41510; 59092</t>
+          <t>40535; 59378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47052; 64623</t>
+          <t>47880; 65466</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32911; 50078</t>
+          <t>33147; 51089</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>128687; 138344</t>
+          <t>128309; 138310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77724; 101781</t>
+          <t>78001; 101065</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91083; 113649</t>
+          <t>89991; 113616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61757; 85534</t>
+          <t>61617; 84072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>240555; 251480</t>
+          <t>239905; 251698</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39436; 56522</t>
+          <t>39986; 56603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56461; 75451</t>
+          <t>57306; 75299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59477; 78426</t>
+          <t>59978; 78507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177345; 186318</t>
+          <t>177362; 186349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49370; 67402</t>
+          <t>49753; 67909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67406; 88260</t>
+          <t>67637; 87409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67622; 89703</t>
+          <t>67778; 89001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>230995; 247227</t>
+          <t>232302; 246963</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93149; 117584</t>
+          <t>93848; 119044</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130032; 157692</t>
+          <t>130428; 156402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132845; 161366</t>
+          <t>132341; 160819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>413272; 431216</t>
+          <t>412465; 431649</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37952; 52775</t>
+          <t>37639; 53939</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40562; 56890</t>
+          <t>40651; 56210</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35242; 51169</t>
+          <t>35190; 51338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176373; 186513</t>
+          <t>175334; 186304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44986; 61601</t>
+          <t>44567; 60331</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46171; 64835</t>
+          <t>46677; 64233</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47099; 65641</t>
+          <t>47153; 65363</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>166612; 178559</t>
+          <t>165963; 177971</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87356; 110286</t>
+          <t>86939; 109781</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90080; 114116</t>
+          <t>91134; 114824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88277; 112399</t>
+          <t>88092; 111541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>347047; 362966</t>
+          <t>347359; 362578</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56308; 77528</t>
+          <t>56927; 79160</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52523; 74273</t>
+          <t>52606; 72875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67722; 89462</t>
+          <t>65851; 88318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149413; 161149</t>
+          <t>149939; 162139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55642; 75256</t>
+          <t>55226; 75176</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59734; 80096</t>
+          <t>59700; 80992</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49449; 69764</t>
+          <t>49591; 69989</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>165529; 177043</t>
+          <t>166776; 176969</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116055; 146256</t>
+          <t>118548; 146690</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117960; 146438</t>
+          <t>118683; 146795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122804; 152654</t>
+          <t>122746; 153613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>320023; 335823</t>
+          <t>320060; 336001</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182877; 216941</t>
+          <t>181145; 217000</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>205564; 239769</t>
+          <t>204644; 239956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>205187; 245939</t>
+          <t>206228; 241106</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>623857; 643158</t>
+          <t>624388; 642736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>208567; 243856</t>
+          <t>208778; 245146</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>239227; 276099</t>
+          <t>240217; 278303</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>216460; 254440</t>
+          <t>214222; 253416</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>708305; 732249</t>
+          <t>709120; 732502</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>401501; 451997</t>
+          <t>399580; 453282</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>454290; 509320</t>
+          <t>454476; 506927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>429534; 483422</t>
+          <t>430455; 483498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1339500; 1368932</t>
+          <t>1340125; 1370764</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>37,39%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>46,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>35,25%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,25; 45,29</t>
+          <t>35,09; 50,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,52; 56,87</t>
+          <t>42,87; 57,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,7; 44,72</t>
+          <t>31,69; 47,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,06; 97,78</t>
+          <t>90,06; 98,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,27; 50,2</t>
+          <t>29,91; 45,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,56; 58,19</t>
+          <t>39,1; 55,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,67; 48,81</t>
+          <t>26,66; 43,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,38; 98,5</t>
+          <t>92,21; 97,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,9; 45,22</t>
+          <t>34,32; 45,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,93; 54,2</t>
+          <t>42,93; 54,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,64; 43,17</t>
+          <t>31,46; 43,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,1; 97,67</t>
+          <t>93,25; 97,71</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>38,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>51,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>45,62%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,0; 45,29</t>
+          <t>34,41; 48,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,43; 58,38</t>
+          <t>44,04; 57,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,48; 51,67</t>
+          <t>38,55; 50,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,1; 97,81</t>
+          <t>91,14; 96,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,35; 48,25</t>
+          <t>32,03; 45,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,76; 56,55</t>
+          <t>43,88; 58,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,66; 50,77</t>
+          <t>39,07; 51,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,83</t>
+          <t>93,38; 98,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 44,8</t>
+          <t>35,6; 45,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46,0; 55,16</t>
+          <t>45,89; 55,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40,44; 49,15</t>
+          <t>40,68; 49,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,57; 96,88</t>
+          <t>93,03; 96,88</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>42,41%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>46,07%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>37,43%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,9; 50,01</t>
+          <t>39,42; 54,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,77; 53,61</t>
+          <t>39,5; 53,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 44,05</t>
+          <t>34,51; 48,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92,09; 97,85</t>
+          <t>89,85; 96,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 53,59</t>
+          <t>35,06; 50,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,97; 55,0</t>
+          <t>38,13; 53,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,49; 49,2</t>
+          <t>31,03; 44,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,57; 96,05</t>
+          <t>90,67; 97,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,44; 49,81</t>
+          <t>40,05; 49,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41,12; 51,81</t>
+          <t>41,53; 51,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,32; 44,72</t>
+          <t>35,32; 44,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,46; 96,51</t>
+          <t>91,27; 95,91</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>42,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>46,74%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,46%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,43; 47,88</t>
+          <t>35,7; 48,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,03; 49,91</t>
+          <t>39,14; 52,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,47; 52,94</t>
+          <t>31,69; 44,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,27; 96,53</t>
+          <t>91,47; 97,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,19; 47,9</t>
+          <t>34,21; 47,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 52,27</t>
+          <t>36,06; 49,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,35; 44,24</t>
+          <t>40,51; 53,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,02; 97,64</t>
+          <t>88,88; 96,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,78; 45,52</t>
+          <t>36,81; 45,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 48,78</t>
+          <t>39,2; 48,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37,76; 47,26</t>
+          <t>37,74; 46,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,65; 96,22</t>
+          <t>91,49; 96,01</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 43,11</t>
+          <t>39,43; 46,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,31</t>
+          <t>44,3; 51,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,25; 45,89</t>
+          <t>37,88; 44,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,73; 96,48</t>
+          <t>93,03; 96,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,5; 46,38</t>
+          <t>36,09; 43,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,59; 51,65</t>
+          <t>43,08; 50,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,51; 44,38</t>
+          <t>38,94; 45,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,06; 96,13</t>
+          <t>93,2; 96,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,93</t>
+          <t>38,83; 43,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,74; 49,91</t>
+          <t>44,8; 49,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,26; 44,1</t>
+          <t>39,31; 44,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,98</t>
+          <t>93,67; 95,82</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49766</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56308</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121366</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>39335</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>45627</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>31755</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>111992</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>49766</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56308</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41150</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>135087</t>
+          <t>115971</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>247080</t>
+          <t>237338</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31830; 47647</t>
+          <t>41504; 59300</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37410; 55236</t>
+          <t>48226; 65029</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24955; 40284</t>
+          <t>33168; 49415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107971; 114675</t>
+          <t>113387; 123801</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40535; 59378</t>
+          <t>31465; 48086</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47880; 65466</t>
+          <t>37980; 53922</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33147; 51089</t>
+          <t>24017; 39356</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>128309; 138310</t>
+          <t>111636; 118568</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78001; 101065</t>
+          <t>76712; 101435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89991; 113616</t>
+          <t>89999; 113791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61617; 84072</t>
+          <t>61270; 85451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>239905; 251698</t>
+          <t>230311; 241332</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>268</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58073</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77801</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77990</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224179</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>47853</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>66041</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>69312</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>182854</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>58073</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77801</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77990</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>177475</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>423869</t>
+          <t>401654</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39986; 56603</t>
+          <t>48424; 67801</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57306; 75299</t>
+          <t>68069; 88309</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59978; 78507</t>
+          <t>67573; 88767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>177362; 186349</t>
+          <t>216189; 229845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49753; 67909</t>
+          <t>40027; 57110</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67637; 87409</t>
+          <t>56595; 74868</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67778; 89001</t>
+          <t>59358; 78784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>232302; 246963</t>
+          <t>172210; 180989</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93848; 119044</t>
+          <t>94584; 120133</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130428; 156402</t>
+          <t>130126; 156067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132341; 160819</t>
+          <t>133130; 161831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>412465; 431649</t>
+          <t>392219; 408484</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>215</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52737</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54699</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56216</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157707</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>45742</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>48307</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>43630</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>182173</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>52737</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54699</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56216</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>173656</t>
+          <t>148579</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>355829</t>
+          <t>306286</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37639; 53939</t>
+          <t>44378; 61387</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40651; 56210</t>
+          <t>46128; 62899</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35190; 51338</t>
+          <t>45852; 64357</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175334; 186304</t>
+          <t>151261; 162127</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44567; 60331</t>
+          <t>37814; 53985</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46677; 64233</t>
+          <t>39977; 56281</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47153; 65363</t>
+          <t>36169; 51912</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>165963; 177971</t>
+          <t>142400; 152403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86939; 109781</t>
+          <t>88274; 109651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91134; 114824</t>
+          <t>92048; 115040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88092; 111541</t>
+          <t>88091; 111578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>347359; 362578</t>
+          <t>296989; 312088</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>225</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>65657</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70265</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59262</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>160945</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>67215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>62419</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>77977</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>156648</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65657</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70265</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59262</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>172412</t>
+          <t>155454</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>329061</t>
+          <t>316398</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56927; 79160</t>
+          <t>56023; 76657</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52606; 72875</t>
+          <t>60648; 81325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65851; 88318</t>
+          <t>50142; 69818</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149939; 162139</t>
+          <t>154934; 165014</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55226; 75176</t>
+          <t>56565; 78916</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59700; 80992</t>
+          <t>52652; 72757</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49591; 69989</t>
+          <t>67586; 89763</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>166776; 176969</t>
+          <t>148564; 160634</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118548; 146690</t>
+          <t>118643; 147022</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>118683; 146795</t>
+          <t>117974; 147027</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122746; 153613</t>
+          <t>122679; 151868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>320060; 336001</t>
+          <t>307892; 323093</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>893</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>633667</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>597478</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1355836</t>
+          <t>1261676</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>181145; 217000</t>
+          <t>208384; 245623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204644; 239956</t>
+          <t>238688; 276489</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206228; 241106</t>
+          <t>216293; 255101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>624388; 642736</t>
+          <t>651951; 673502</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>208778; 245146</t>
+          <t>181684; 218077</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>240217; 278303</t>
+          <t>205485; 239569</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>214222; 253416</t>
+          <t>204609; 239933</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>709120; 732502</t>
+          <t>586887; 605754</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>399580; 453282</t>
+          <t>400649; 450187</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>454476; 506927</t>
+          <t>455074; 505661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>430455; 483498</t>
+          <t>431014; 485340</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1340125; 1370764</t>
+          <t>1246306; 1274903</t>
         </is>
       </c>
     </row>
